--- a/data/trans_dic/P2A_fisi_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación, discapacidad física</t>
+          <t>Hogares con personas con limitación, discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,22</t>
+          <t>0,0; 5,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>0,0; 7,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,34</t>
+          <t>0,0; 10,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,05</t>
+          <t>0,54; 4,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,36</t>
+          <t>0,98; 9,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,5</t>
+          <t>0,0; 7,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,68</t>
+          <t>0,0; 7,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,65</t>
+          <t>0,77; 6,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,26</t>
+          <t>0,93; 5,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,35</t>
+          <t>0,55; 4,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,0</t>
+          <t>0,42; 6,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,59</t>
+          <t>0,98; 4,7</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,71</t>
+          <t>0,83; 7,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,11</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 5,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,61</t>
+          <t>0,77; 6,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,14</t>
+          <t>0,0; 7,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,72</t>
+          <t>0,0; 7,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,59</t>
+          <t>0,0; 5,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 9,72</t>
+          <t>1,67; 9,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,4</t>
+          <t>0,85; 5,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,57</t>
+          <t>0,59; 5,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,83</t>
+          <t>0,37; 4,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,0</t>
+          <t>1,88; 6,85</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,9</t>
+          <t>0,0; 6,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,05</t>
+          <t>1,23; 9,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 13,01</t>
+          <t>1,49; 12,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,76</t>
+          <t>0,73; 6,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,04</t>
+          <t>1,14; 10,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 12,34</t>
+          <t>1,07; 11,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,0</t>
+          <t>1,88; 13,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,68</t>
+          <t>0,54; 4,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,94</t>
+          <t>1,46; 6,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 8,76</t>
+          <t>1,74; 8,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,68</t>
+          <t>2,52; 9,91</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,58</t>
+          <t>0,85; 5,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,95</t>
+          <t>0,94; 5,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 7,05</t>
+          <t>2,15; 7,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,92</t>
+          <t>1,52; 6,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,23</t>
+          <t>1,6; 6,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,96</t>
+          <t>1,05; 5,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 13,26</t>
+          <t>4,01; 14,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,05</t>
+          <t>1,1; 3,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,91</t>
+          <t>1,67; 5,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,28</t>
+          <t>1,37; 4,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,17</t>
+          <t>3,34; 8,85</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,7</t>
+          <t>1,14; 11,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,15</t>
+          <t>0,79; 7,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 8,2</t>
+          <t>1,22; 7,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 15,37</t>
+          <t>5,81; 15,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 10,4</t>
+          <t>2,36; 11,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 8,37</t>
+          <t>1,46; 7,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,96</t>
+          <t>0,66; 6,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 11,55</t>
+          <t>4,07; 11,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,3</t>
+          <t>2,59; 8,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,26</t>
+          <t>1,67; 6,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,42</t>
+          <t>1,23; 5,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 11,39</t>
+          <t>5,86; 11,74</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,91</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 11,68</t>
+          <t>1,31; 13,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,16</t>
+          <t>0,0; 6,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,92; 15,06</t>
+          <t>3,66; 14,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,51</t>
+          <t>0,89; 8,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 10,62</t>
+          <t>1,79; 10,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 17,1</t>
+          <t>4,55; 18,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,45</t>
+          <t>0,47; 4,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,59; 9,03</t>
+          <t>2,58; 8,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,05</t>
+          <t>0,44; 4,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 13,77</t>
+          <t>5,45; 13,58</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,06</t>
+          <t>0,98; 2,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,25</t>
+          <t>1,76; 4,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,06</t>
+          <t>1,66; 4,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,7</t>
+          <t>3,89; 6,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,87</t>
+          <t>2,24; 4,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,06</t>
+          <t>2,43; 4,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,5</t>
+          <t>1,36; 3,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,23</t>
+          <t>4,53; 8,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,47</t>
+          <t>1,96; 3,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,21</t>
+          <t>2,42; 4,22</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,36</t>
+          <t>1,74; 3,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,06</t>
+          <t>4,5; 7,04</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con limitación, discapacidad física (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2668</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1674</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3635</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2599</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3071</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5538</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4295</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4299</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6806</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>559; 5050</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>699; 6795</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5148</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5600</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1052; 9168</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1414; 8113</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>742; 6337</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>601; 8946</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2373; 11345</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2860</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1393</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1546</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4154</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3345</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2954</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2443</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>7015</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>573; 5381</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5063</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>726; 5992</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4829</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5417</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5392</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1592; 9078</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1157; 7311</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>788; 7052</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>643; 7188</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3586; 13034</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2758</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3419</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3594</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4725</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4750</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3142</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4551</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>604; 4471</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>775; 6407</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>610; 5523</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>773; 7260</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>652; 6959</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1203; 8698</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>774; 6860</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1962; 8766</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1915; 8967</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2911; 11466</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3461</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4462</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9069</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5453</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5498</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4154</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>15610</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6774</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>8959</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>24678</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4758</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1162; 7884</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1557; 9416</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4714; 15718</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2263; 10350</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2586; 10033</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1799; 9189</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>8760; 30766</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3291; 11852</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>4985; 14901</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4601; 15068</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>14605; 38688</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2965</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2977</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3475</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3444</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2128</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>11479</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7656</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6421</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5604</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>23427</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>785; 7604</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>741; 7202</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1242; 7593</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6935; 17998</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1991; 9482</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1339; 7322</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>655; 6287</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>6612; 18507</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3982; 13052</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3095; 12068</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2468; 10422</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>16516; 33107</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2772</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5585</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3891</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>6834</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2631</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>6664</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>12419</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3335</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>708; 7049</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3685</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2520; 9948</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>642; 6066</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1322; 7432</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3597</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3276; 13132</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>698; 6296</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>3299; 11183</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>570; 5356</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>7684; 19141</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>8948</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13156</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>13758</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>34124</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>18269</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>19165</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>12645</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>45306</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>27217</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>32322</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>26402</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>79429</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>4948; 14629</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>8417; 21328</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>8712; 21369</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>25574; 45524</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>11828; 25565</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>13082; 26457</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7733; 19740</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>33944; 61538</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>20228; 37024</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>24529; 42798</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>19018; 37158</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>63341; 99118</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_fisi_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,34</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,5</t>
+          <t>0,0; 10,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,83</t>
+          <t>0,53; 4,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,49</t>
+          <t>0,97; 9,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,01</t>
+          <t>0,0; 6,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,16</t>
+          <t>0,0; 8,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,7</t>
+          <t>0,73; 6,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,33</t>
+          <t>0,89; 5,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,71</t>
+          <t>0,54; 5,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,25</t>
+          <t>0,42; 6,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,7</t>
+          <t>0,91; 4,36</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,83</t>
+          <t>0,83; 7,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 7,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,32</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1,04; 7,15</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,16</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,35</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 5,78</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,77; 6,33</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,16</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,91</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,79</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 9,5</t>
+          <t>1,7; 9,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,37</t>
+          <t>0,93; 5,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,27</t>
+          <t>0,59; 4,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,1</t>
+          <t>0,37; 4,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,85</t>
+          <t>1,76; 6,55</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,84</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 9,08</t>
+          <t>1,22; 10,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 12,35</t>
+          <t>1,44; 12,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,58</t>
+          <t>0,73; 6,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 10,68</t>
+          <t>1,95; 11,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 11,41</t>
+          <t>1,19; 11,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 13,62</t>
+          <t>2,09; 13,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,82</t>
+          <t>0,54; 4,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,52</t>
+          <t>1,52; 6,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 8,13</t>
+          <t>1,9; 8,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,91</t>
+          <t>2,61; 10,17</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,78</t>
+          <t>0,88; 5,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,68</t>
+          <t>0,95; 5,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,18</t>
+          <t>2,01; 6,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,97</t>
+          <t>1,74; 6,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,22</t>
+          <t>1,67; 6,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,38</t>
+          <t>0,89; 5,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 14,1</t>
+          <t>3,63; 13,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,95</t>
+          <t>1,13; 3,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,0</t>
+          <t>1,73; 5,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,48</t>
+          <t>1,33; 4,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,85</t>
+          <t>3,63; 9,51</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 11,0</t>
+          <t>1,14; 10,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,71</t>
+          <t>1,07; 8,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,47</t>
+          <t>1,24; 7,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 15,07</t>
+          <t>6,19; 15,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 11,22</t>
+          <t>2,26; 10,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,96</t>
+          <t>1,45; 8,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,34</t>
+          <t>0,65; 5,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 11,38</t>
+          <t>4,14; 11,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,49</t>
+          <t>2,42; 8,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,51</t>
+          <t>1,79; 6,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,19</t>
+          <t>1,32; 5,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 11,74</t>
+          <t>5,76; 11,57</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 13,08</t>
+          <t>1,26; 11,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,11</t>
+          <t>0,0; 7,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,66; 14,44</t>
+          <t>3,78; 14,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,38</t>
+          <t>0,88; 8,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 10,04</t>
+          <t>1,86; 10,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 6,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,55; 18,24</t>
+          <t>4,51; 16,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,28</t>
+          <t>0,47; 4,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,74</t>
+          <t>2,59; 9,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,18</t>
+          <t>0,44; 4,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,45; 13,58</t>
+          <t>5,38; 13,28</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,91</t>
+          <t>1,01; 3,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,47</t>
+          <t>1,8; 4,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,08</t>
+          <t>1,67; 4,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 6,92</t>
+          <t>3,79; 6,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,84</t>
+          <t>2,3; 5,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,92</t>
+          <t>2,46; 5,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,46</t>
+          <t>1,3; 3,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,21</t>
+          <t>4,47; 8,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,59</t>
+          <t>1,89; 3,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,22</t>
+          <t>2,41; 4,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,4</t>
+          <t>1,63; 3,26</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,04</t>
+          <t>4,61; 7,01</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4295</t>
+          <t>0; 4534</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4299</t>
+          <t>0; 3986</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6806</t>
+          <t>0; 6774</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>559; 5050</t>
+          <t>557; 4997</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>699; 6795</t>
+          <t>696; 6664</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5148</t>
+          <t>0; 4835</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5600</t>
+          <t>0; 6285</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1052; 9168</t>
+          <t>1005; 8835</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1414; 8113</t>
+          <t>1357; 8697</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>742; 6337</t>
+          <t>726; 6751</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>601; 8946</t>
+          <t>600; 8827</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2373; 11345</t>
+          <t>2192; 10532</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>573; 5381</t>
+          <t>573; 4840</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5063</t>
+          <t>0; 4678</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4757</t>
+          <t>0; 4375</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>726; 5992</t>
+          <t>987; 6768</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4829</t>
+          <t>0; 4835</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5417</t>
+          <t>0; 5034</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5392</t>
+          <t>0; 5375</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1592; 9078</t>
+          <t>1624; 9172</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1157; 7311</t>
+          <t>1270; 7543</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>788; 7052</t>
+          <t>785; 6577</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>643; 7188</t>
+          <t>641; 7081</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3586; 13034</t>
+          <t>3346; 12459</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3142</t>
+          <t>0; 3925</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4551</t>
+          <t>0; 4016</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>604; 4471</t>
+          <t>602; 4997</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>775; 6407</t>
+          <t>747; 6412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>610; 5523</t>
+          <t>614; 5566</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>773; 7260</t>
+          <t>1324; 7850</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>652; 6959</t>
+          <t>729; 6897</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1203; 8698</t>
+          <t>1336; 8569</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>774; 6860</t>
+          <t>772; 6497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1962; 8766</t>
+          <t>2039; 9372</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1915; 8967</t>
+          <t>2095; 9375</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2911; 11466</t>
+          <t>3016; 11765</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4758</t>
+          <t>0; 4018</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1162; 7884</t>
+          <t>1195; 7833</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1557; 9416</t>
+          <t>1568; 9057</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4714; 15718</t>
+          <t>4388; 15157</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2263; 10350</t>
+          <t>2582; 10157</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2586; 10033</t>
+          <t>2698; 10144</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1799; 9189</t>
+          <t>1527; 8851</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8760; 30766</t>
+          <t>7932; 29276</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3291; 11852</t>
+          <t>3385; 11605</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4985; 14901</t>
+          <t>5155; 15016</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4601; 15068</t>
+          <t>4463; 14265</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14605; 38688</t>
+          <t>15853; 41567</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>785; 7604</t>
+          <t>791; 7005</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>741; 7202</t>
+          <t>996; 7615</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1242; 7593</t>
+          <t>1257; 7671</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6935; 17998</t>
+          <t>7390; 18782</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1991; 9482</t>
+          <t>1914; 8802</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1339; 7322</t>
+          <t>1336; 7643</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>655; 6287</t>
+          <t>646; 5823</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6612; 18507</t>
+          <t>6735; 18900</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3982; 13052</t>
+          <t>3726; 12746</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3095; 12068</t>
+          <t>3311; 11711</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2468; 10422</t>
+          <t>2643; 10175</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16516; 33107</t>
+          <t>16249; 32645</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3335</t>
+          <t>0; 2942</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>708; 7049</t>
+          <t>677; 6226</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3685</t>
+          <t>0; 4476</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2520; 9948</t>
+          <t>2603; 9926</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>642; 6066</t>
+          <t>639; 5863</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1322; 7432</t>
+          <t>1377; 7821</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3597</t>
+          <t>0; 4584</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3276; 13132</t>
+          <t>3249; 11872</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>698; 6296</t>
+          <t>696; 6047</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3299; 11183</t>
+          <t>3315; 12096</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>570; 5356</t>
+          <t>562; 5602</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7684; 19141</t>
+          <t>7583; 18710</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4948; 14629</t>
+          <t>5072; 15464</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8417; 21328</t>
+          <t>8595; 20541</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8712; 21369</t>
+          <t>8777; 20998</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25574; 45524</t>
+          <t>24959; 45215</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11828; 25565</t>
+          <t>12140; 26620</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13082; 26457</t>
+          <t>13216; 27261</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7733; 19740</t>
+          <t>7420; 20023</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>33944; 61538</t>
+          <t>33521; 61740</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20228; 37024</t>
+          <t>19520; 36032</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24529; 42798</t>
+          <t>24398; 42589</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19018; 37158</t>
+          <t>17854; 35661</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>63341; 99118</t>
+          <t>64911; 98632</t>
         </is>
       </c>
     </row>
